--- a/data/trans_bre/P6901-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 19,3</t>
+          <t>-16,19; 20,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 15,26</t>
+          <t>-24,76; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 29,14</t>
+          <t>-12,09; 30,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 34,01</t>
+          <t>-4,15; 32,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 37,58</t>
+          <t>-25,55; 42,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 29,04</t>
+          <t>-33,67; 28,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 70,84</t>
+          <t>-18,33; 74,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 108,31</t>
+          <t>-7,14; 94,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 53,5</t>
+          <t>15,13; 53,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 22,12</t>
+          <t>-27,13; 22,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 31,67</t>
+          <t>-6,23; 33,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 19,82</t>
+          <t>-21,79; 20,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,25; 153,25</t>
+          <t>25,11; 151,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 33,39</t>
+          <t>-32,69; 32,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 49,95</t>
+          <t>-6,63; 55,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 46,7</t>
+          <t>-32,79; 50,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 17,31</t>
+          <t>-25,93; 17,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 32,9</t>
+          <t>4,19; 33,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 37,32</t>
+          <t>-13,06; 37,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 29,08</t>
+          <t>-10,48; 30,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 22,58</t>
+          <t>-32,01; 22,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 54,27</t>
+          <t>6,05; 54,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 62,06</t>
+          <t>-12,39; 64,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 47,74</t>
+          <t>-13,4; 49,77</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 4,51</t>
+          <t>-22,55; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 16,23</t>
+          <t>-7,46; 17,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 21,29</t>
+          <t>0,94; 21,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 6,59</t>
+          <t>-13,17; 5,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 5,81</t>
+          <t>-27,4; 6,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 22,69</t>
+          <t>-9,23; 24,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 28,96</t>
+          <t>1,22; 29,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 8,14</t>
+          <t>-15,25; 6,94</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 17,32</t>
+          <t>-5,79; 17,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 12,91</t>
+          <t>-22,32; 11,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 19,87</t>
+          <t>-3,65; 19,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 16,49</t>
+          <t>-11,02; 16,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 23,07</t>
+          <t>-6,31; 24,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 16,34</t>
+          <t>-24,71; 14,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 27,43</t>
+          <t>-3,91; 26,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 20,95</t>
+          <t>-11,51; 20,75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,7</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,94; 9,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,46; 10,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,66; 17,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,18; 14,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,03; 13,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,45; 15,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,84; 24,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,6; 20,9</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,44</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 9,7</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 11,08</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 16,95</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 14,21</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-5,28; 13,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-5,34; 15,56</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,63; 24,51</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-1,59; 20,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6901-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,04</t>
+          <t>11,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 20,89</t>
+          <t>-18,24; 21,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 15,88</t>
+          <t>-24,96; 14,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 30,37</t>
+          <t>-11,92; 29,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 32,97</t>
+          <t>-5,43; 30,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 42,39</t>
+          <t>-27,71; 41,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 28,68</t>
+          <t>-34,87; 26,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 74,9</t>
+          <t>-18,53; 69,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 94,36</t>
+          <t>-8,64; 79,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,29%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 53,08</t>
+          <t>13,61; 53,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 22,13</t>
+          <t>-27,43; 23,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 33,31</t>
+          <t>-3,01; 33,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 20,87</t>
+          <t>-18,84; 21,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,11; 151,55</t>
+          <t>22,89; 154,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 32,79</t>
+          <t>-32,63; 33,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 55,56</t>
+          <t>-3,53; 55,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 50,14</t>
+          <t>-28,34; 50,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,48</t>
+          <t>9,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 17,36</t>
+          <t>-26,14; 17,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 33,09</t>
+          <t>3,48; 33,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 37,67</t>
+          <t>-13,58; 37,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 30,15</t>
+          <t>-10,29; 27,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 22,59</t>
+          <t>-32,63; 22,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 54,2</t>
+          <t>5,6; 54,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 64,22</t>
+          <t>-15,71; 63,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 49,77</t>
+          <t>-12,45; 46,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,73</t>
+          <t>-3,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,48%</t>
+          <t>-4,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 4,7</t>
+          <t>-23,81; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 17,18</t>
+          <t>-6,7; 17,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 21,41</t>
+          <t>1,56; 21,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 5,61</t>
+          <t>-13,91; 5,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 6,0</t>
+          <t>-28,45; 5,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 24,61</t>
+          <t>-8,17; 24,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 29,35</t>
+          <t>1,88; 28,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,94</t>
+          <t>-15,66; 7,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 17,84</t>
+          <t>-6,32; 16,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 11,54</t>
+          <t>-21,27; 12,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 19,62</t>
+          <t>-6,04; 18,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 16,41</t>
+          <t>-4,75; 13,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 24,17</t>
+          <t>-6,49; 20,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 14,49</t>
+          <t>-22,75; 16,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 26,36</t>
+          <t>-6,73; 25,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 20,75</t>
+          <t>-4,92; 16,26</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,67</t>
+          <t>-3,69; 9,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,73</t>
+          <t>-4,49; 11,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,31</t>
+          <t>3,19; 17,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 14,31</t>
+          <t>-2,97; 8,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,3</t>
+          <t>-4,71; 13,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,32</t>
+          <t>-6,04; 16,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 24,41</t>
+          <t>3,99; 24,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 20,9</t>
+          <t>-3,77; 12,55</t>
         </is>
       </c>
     </row>
